--- a/Team-Data/2007-08/12-23-2007-08.xlsx
+++ b/Team-Data/2007-08/12-23-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>15</v>
@@ -772,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>6</v>
@@ -796,13 +863,13 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L3" t="n">
         <v>7.4</v>
@@ -873,25 +940,25 @@
         <v>19.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P3" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
         <v>0.774</v>
       </c>
       <c r="R3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
         <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U3" t="n">
         <v>22.8</v>
@@ -900,28 +967,28 @@
         <v>15.5</v>
       </c>
       <c r="W3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>6</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -957,7 +1024,7 @@
         <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>9</v>
@@ -966,16 +1033,16 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
@@ -987,7 +1054,7 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
@@ -1157,7 +1224,7 @@
         <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
         <v>9</v>
@@ -1169,7 +1236,7 @@
         <v>24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>15</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>24</v>
@@ -1333,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
         <v>13</v>
@@ -1351,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,82 +1474,82 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
         <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="O6" t="n">
         <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.723</v>
       </c>
       <c r="R6" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U6" t="n">
         <v>19.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>4.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB6" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
@@ -1494,10 +1561,10 @@
         <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1509,28 +1576,28 @@
         <v>24</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>16</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
         <v>27</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
         <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
         <v>24</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>5</v>
@@ -1664,10 +1731,10 @@
         <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1753,97 +1820,97 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.593</v>
+        <v>0.577</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J8" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M8" t="n">
-        <v>19.1</v>
+        <v>18.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="O8" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="P8" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R8" t="n">
         <v>11.3</v>
       </c>
       <c r="S8" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>44.1</v>
+        <v>43.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AB8" t="n">
         <v>106.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1858,10 +1925,10 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,22 +1937,22 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,16 +1964,16 @@
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.741</v>
+        <v>0.731</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.35</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R9" t="n">
         <v>11.8</v>
@@ -1989,7 +2056,7 @@
         <v>23.1</v>
       </c>
       <c r="V9" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="W9" t="n">
         <v>6.9</v>
@@ -1998,22 +2065,22 @@
         <v>5.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,31 +2095,31 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>14</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
@@ -2073,10 +2140,10 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
         <v>7</v>
@@ -2085,7 +2152,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -2117,85 +2184,85 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="J10" t="n">
-        <v>89.2</v>
+        <v>89.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M10" t="n">
-        <v>26.7</v>
+        <v>27.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O10" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P10" t="n">
         <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
         <v>9</v>
       </c>
       <c r="X10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
         <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.2</v>
+        <v>108.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>9</v>
@@ -2207,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2234,34 +2301,34 @@
         <v>17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
         <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.464</v>
+        <v>0.481</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="J11" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L11" t="n">
         <v>6.6</v>
@@ -2329,7 +2396,7 @@
         <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.333</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
         <v>16.5</v>
@@ -2338,25 +2405,25 @@
         <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="R11" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S11" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
         <v>5.5</v>
@@ -2365,34 +2432,34 @@
         <v>4.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
         <v>17</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>11</v>
@@ -2404,10 +2471,10 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
         <v>26</v>
@@ -2419,37 +2486,37 @@
         <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS11" t="n">
         <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
         <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>0.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2607,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>3</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2771,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2789,13 +2856,13 @@
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -2845,61 +2912,61 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.63</v>
+        <v>0.615</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S14" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
@@ -2908,31 +2975,31 @@
         <v>4.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>106.3</v>
       </c>
       <c r="AC14" t="n">
         <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2944,19 +3011,19 @@
         <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2965,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
@@ -2977,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -2986,16 +3053,16 @@
         <v>15</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
         <v>11</v>
@@ -3126,7 +3193,7 @@
         <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
         <v>6</v>
@@ -3138,13 +3205,13 @@
         <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -3287,19 +3354,19 @@
         <v>-4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>23</v>
@@ -3323,16 +3390,16 @@
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
@@ -3350,7 +3417,7 @@
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ16" t="n">
         <v>11</v>
@@ -3359,7 +3426,7 @@
         <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3536,22 @@
         <v>-4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -3511,13 +3578,13 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
         <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,7 +3733,7 @@
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3693,7 +3760,7 @@
         <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
         <v>23</v>
@@ -3705,7 +3772,7 @@
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW18" t="n">
         <v>19</v>
@@ -3714,7 +3781,7 @@
         <v>22</v>
       </c>
       <c r="AY18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3866,13 +3933,13 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>17</v>
@@ -3881,7 +3948,7 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
@@ -3890,7 +3957,7 @@
         <v>29</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>7</v>
@@ -4024,7 +4091,7 @@
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>4</v>
@@ -4042,10 +4109,10 @@
         <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4054,7 +4121,7 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -4072,10 +4139,10 @@
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>0.296</v>
+        <v>0.308</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="J21" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.432</v>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
         <v>16.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7</v>
+        <v>0.699</v>
       </c>
       <c r="R21" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="U21" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="V21" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W21" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z21" t="n">
         <v>21.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4221,31 +4288,31 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
         <v>17</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
         <v>29</v>
       </c>
       <c r="AR21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4254,7 +4321,7 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,7 +4333,7 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4301,55 +4368,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
         <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.621</v>
+        <v>0.643</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.461</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M22" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.709</v>
+        <v>0.712</v>
       </c>
       <c r="R22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S22" t="n">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="U22" t="n">
         <v>21.2</v>
@@ -4358,7 +4425,7 @@
         <v>15.5</v>
       </c>
       <c r="W22" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X22" t="n">
         <v>4.5</v>
@@ -4373,31 +4440,31 @@
         <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>6</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH22" t="n">
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>11</v>
@@ -4412,13 +4479,13 @@
         <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4427,16 +4494,16 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
@@ -4454,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4561,22 +4628,22 @@
         <v>-1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
         <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>19</v>
@@ -4591,7 +4658,7 @@
         <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
@@ -4603,7 +4670,7 @@
         <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS23" t="n">
         <v>22</v>
@@ -4615,19 +4682,19 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>5.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
         <v>4</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>-1.4</v>
       </c>
       <c r="AD25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE25" t="n">
         <v>9</v>
       </c>
-      <c r="AE25" t="n">
-        <v>11</v>
-      </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="n">
         <v>26</v>
@@ -4970,16 +5037,16 @@
         <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU25" t="n">
         <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -5029,91 +5096,91 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
         <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.423</v>
+        <v>0.44</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M26" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O26" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="P26" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.787</v>
+        <v>0.795</v>
       </c>
       <c r="R26" t="n">
         <v>10.1</v>
       </c>
       <c r="S26" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="T26" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="U26" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="V26" t="n">
         <v>16.1</v>
       </c>
       <c r="W26" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AB26" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
         <v>20</v>
@@ -5125,7 +5192,7 @@
         <v>24</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
@@ -5134,28 +5201,28 @@
         <v>17</v>
       </c>
       <c r="AM26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>4</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR26" t="n">
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5164,13 +5231,13 @@
         <v>24</v>
       </c>
       <c r="AW26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ26" t="n">
         <v>23</v>
@@ -5179,7 +5246,7 @@
         <v>3</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>6.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL27" t="n">
         <v>4</v>
@@ -5346,10 +5413,10 @@
         <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5538,19 @@
         <v>-6.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5528,7 +5595,7 @@
         <v>30</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
@@ -5674,7 +5741,7 @@
         <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>7</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5868,28 +5935,28 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>2</v>
       </c>
       <c r="AQ30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT30" t="n">
         <v>19</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6029,7 +6096,7 @@
         <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
         <v>10</v>
@@ -6041,10 +6108,10 @@
         <v>17</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN31" t="n">
         <v>22</v>
@@ -6059,13 +6126,13 @@
         <v>6</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
         <v>11</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU31" t="n">
         <v>26</v>
@@ -6074,7 +6141,7 @@
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-23-2007-08</t>
+          <t>2007-12-23</t>
         </is>
       </c>
     </row>
